--- a/Team-Data/2007-08/3-8-2007-08.xlsx
+++ b/Team-Data/2007-08/3-8-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -688,10 +755,10 @@
         <v>4.1</v>
       </c>
       <c r="M2" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O2" t="n">
         <v>21.3</v>
@@ -703,10 +770,10 @@
         <v>0.775</v>
       </c>
       <c r="R2" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T2" t="n">
         <v>42.3</v>
@@ -715,7 +782,7 @@
         <v>21.3</v>
       </c>
       <c r="V2" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W2" t="n">
         <v>7.5</v>
@@ -724,37 +791,37 @@
         <v>5.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB2" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
         <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -769,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
@@ -778,7 +845,7 @@
         <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -787,7 +854,7 @@
         <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
         <v>17</v>
@@ -796,7 +863,7 @@
         <v>26</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>3</v>
@@ -805,10 +872,10 @@
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>24</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
         <v>76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.476</v>
+        <v>0.474</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
+        <v>0.385</v>
       </c>
       <c r="O3" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
         <v>41.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V3" t="n">
         <v>15.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.5</v>
@@ -912,16 +979,16 @@
         <v>22.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,19 +1012,19 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN3" t="n">
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -969,13 +1036,13 @@
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -987,10 +1054,10 @@
         <v>17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -1025,43 +1092,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.381</v>
+        <v>0.371</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O4" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0.71</v>
@@ -1070,7 +1137,7 @@
         <v>11.3</v>
       </c>
       <c r="S4" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
         <v>40.8</v>
@@ -1091,49 +1158,49 @@
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
         <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="AD4" t="n">
         <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
@@ -1148,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>24</v>
@@ -1163,7 +1230,7 @@
         <v>14</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1352,22 @@
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF5" t="n">
         <v>21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1351,10 +1418,10 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.571</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,13 +1474,13 @@
         <v>36.2</v>
       </c>
       <c r="J6" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K6" t="n">
         <v>0.441</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
         <v>19.3</v>
@@ -1431,16 +1498,16 @@
         <v>0.72</v>
       </c>
       <c r="R6" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="U6" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V6" t="n">
         <v>14.2</v>
@@ -1449,22 +1516,22 @@
         <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
         <v>4.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD6" t="n">
         <v>3</v>
@@ -1482,22 +1549,22 @@
         <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>20</v>
@@ -1509,10 +1576,10 @@
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>5</v>
@@ -1524,16 +1591,16 @@
         <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
@@ -1542,7 +1609,7 @@
         <v>16</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.635</v>
+        <v>0.629</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1598,31 +1665,31 @@
         <v>5.9</v>
       </c>
       <c r="M7" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.353</v>
+        <v>0.348</v>
       </c>
       <c r="O7" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V7" t="n">
         <v>12.9</v>
@@ -1637,40 +1704,40 @@
         <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
         <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>19</v>
@@ -1679,10 +1746,10 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -1694,13 +1761,13 @@
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
         <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV7" t="n">
         <v>4</v>
@@ -1718,7 +1785,7 @@
         <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.597</v>
+        <v>0.607</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,7 +1838,7 @@
         <v>39.1</v>
       </c>
       <c r="J8" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.459</v>
@@ -1780,10 +1847,10 @@
         <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O8" t="n">
         <v>22.9</v>
@@ -1795,22 +1862,22 @@
         <v>0.753</v>
       </c>
       <c r="R8" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.2</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>7</v>
@@ -1819,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA8" t="n">
         <v>24</v>
@@ -1828,10 +1895,10 @@
         <v>107.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,19 +1940,19 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>15</v>
@@ -2058,7 +2125,7 @@
         <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="J10" t="n">
-        <v>89.3</v>
+        <v>89.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L10" t="n">
         <v>9.6</v>
@@ -2147,34 +2214,34 @@
         <v>27.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P10" t="n">
         <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R10" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
         <v>42.3</v>
       </c>
       <c r="U10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X10" t="n">
         <v>4.6</v>
@@ -2189,13 +2256,13 @@
         <v>21.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.8</v>
+        <v>110.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2204,7 +2271,7 @@
         <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -2225,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2237,13 +2304,13 @@
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -2299,46 +2366,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.677</v>
+        <v>0.672</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
         <v>81.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R11" t="n">
         <v>12</v>
@@ -2350,7 +2417,7 @@
         <v>44.5</v>
       </c>
       <c r="U11" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V11" t="n">
         <v>14.4</v>
@@ -2365,40 +2432,40 @@
         <v>4.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="AC11" t="n">
         <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
         <v>11</v>
@@ -2407,16 +2474,16 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
         <v>10</v>
@@ -2425,7 +2492,7 @@
         <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
@@ -2443,16 +2510,16 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="n">
         <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>0.381</v>
+        <v>0.387</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2502,7 +2569,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>9</v>
@@ -2511,25 +2578,25 @@
         <v>24.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>22.7</v>
@@ -2541,19 +2608,19 @@
         <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z12" t="n">
         <v>23.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.9</v>
+        <v>103</v>
       </c>
       <c r="AC12" t="n">
         <v>-2.5</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2592,10 +2659,10 @@
         <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
@@ -2619,22 +2686,22 @@
         <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,34 +2748,34 @@
         <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K13" t="n">
         <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="N13" t="n">
         <v>0.331</v>
       </c>
       <c r="O13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
         <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="R13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T13" t="n">
         <v>40.2</v>
@@ -2717,31 +2784,31 @@
         <v>21.4</v>
       </c>
       <c r="V13" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA13" t="n">
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AC13" t="n">
         <v>-5.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2774,7 +2841,7 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -2783,7 +2850,7 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
         <v>16</v>
@@ -2798,19 +2865,19 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2956,7 +3023,7 @@
         <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2971,10 +3038,10 @@
         <v>1</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>16</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.242</v>
+        <v>0.246</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L15" t="n">
         <v>7.6</v>
@@ -3057,13 +3124,13 @@
         <v>21.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0.734</v>
@@ -3072,10 +3139,10 @@
         <v>10.2</v>
       </c>
       <c r="S15" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T15" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U15" t="n">
         <v>19.4</v>
@@ -3084,10 +3151,10 @@
         <v>15.8</v>
       </c>
       <c r="W15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.8</v>
@@ -3096,22 +3163,22 @@
         <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>28</v>
@@ -3123,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK15" t="n">
         <v>17</v>
@@ -3150,10 +3217,10 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>27</v>
@@ -3165,13 +3232,13 @@
         <v>27</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
@@ -3180,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J16" t="n">
-        <v>78</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
@@ -3236,22 +3303,22 @@
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="N16" t="n">
         <v>0.344</v>
       </c>
       <c r="O16" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P16" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q16" t="n">
         <v>0.724</v>
       </c>
       <c r="R16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S16" t="n">
         <v>29</v>
@@ -3266,28 +3333,28 @@
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z16" t="n">
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB16" t="n">
         <v>93.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.8</v>
+        <v>-7.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3317,10 +3384,10 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
         <v>19</v>
@@ -3341,7 +3408,7 @@
         <v>22</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW16" t="n">
         <v>18</v>
@@ -3356,7 +3423,7 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -3469,25 +3536,25 @@
         <v>-6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK17" t="n">
         <v>19</v>
@@ -3523,7 +3590,7 @@
         <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>23</v>
@@ -3544,7 +3611,7 @@
         <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.226</v>
+        <v>0.213</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3594,25 +3661,25 @@
         <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="P18" t="n">
         <v>20.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.724</v>
+        <v>0.722</v>
       </c>
       <c r="R18" t="n">
         <v>12.1</v>
@@ -3627,10 +3694,10 @@
         <v>19.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W18" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
@@ -3639,19 +3706,19 @@
         <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.4</v>
+        <v>-7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3672,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3705,10 +3772,10 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
         <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.413</v>
+        <v>0.419</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3776,25 +3843,25 @@
         <v>78.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M19" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="N19" t="n">
         <v>0.341</v>
       </c>
       <c r="O19" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P19" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
@@ -3806,10 +3873,10 @@
         <v>42.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V19" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W19" t="n">
         <v>6.5</v>
@@ -3821,16 +3888,16 @@
         <v>4.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AB19" t="n">
         <v>94</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.2</v>
+        <v>-5</v>
       </c>
       <c r="AD19" t="n">
         <v>3</v>
@@ -3839,25 +3906,25 @@
         <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
       </c>
       <c r="AJ19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM19" t="n">
         <v>17</v>
@@ -3869,16 +3936,16 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -3887,7 +3954,7 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
         <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>0.677</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,7 +4022,7 @@
         <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K20" t="n">
         <v>0.461</v>
@@ -3967,22 +4034,22 @@
         <v>20.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="O20" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P20" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.773</v>
+        <v>0.777</v>
       </c>
       <c r="R20" t="n">
         <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T20" t="n">
         <v>42.4</v>
@@ -4003,19 +4070,19 @@
         <v>4.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA20" t="n">
         <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4027,7 +4094,7 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4036,13 +4103,13 @@
         <v>7</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN20" t="n">
         <v>2</v>
@@ -4054,7 +4121,7 @@
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
         <v>13</v>
@@ -4090,7 +4157,7 @@
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -4119,52 +4186,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
         <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
-        <v>0.286</v>
+        <v>0.29</v>
       </c>
       <c r="H21" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J21" t="n">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="K21" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
       </c>
       <c r="M21" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O21" t="n">
         <v>19</v>
       </c>
       <c r="P21" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R21" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
         <v>41.8</v>
@@ -4173,7 +4240,7 @@
         <v>18.5</v>
       </c>
       <c r="V21" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W21" t="n">
         <v>6.1</v>
@@ -4191,7 +4258,7 @@
         <v>21</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="AC21" t="n">
         <v>-6.3</v>
@@ -4209,16 +4276,16 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>16</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO21" t="n">
         <v>12</v>
@@ -4236,10 +4303,10 @@
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
         <v>23</v>
@@ -4251,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
         <v>28</v>
@@ -4266,13 +4333,13 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB21" t="n">
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
         <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.625</v>
+        <v>0.635</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J22" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.473</v>
@@ -4331,34 +4398,34 @@
         <v>24.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O22" t="n">
         <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.727</v>
       </c>
       <c r="R22" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
         <v>42.2</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V22" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W22" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X22" t="n">
         <v>4.2</v>
@@ -4373,10 +4440,10 @@
         <v>23.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4385,16 +4452,16 @@
         <v>8</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4412,28 +4479,28 @@
         <v>6</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>13</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
         <v>26</v>
@@ -4445,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
         <v>5</v>
@@ -4624,7 +4691,7 @@
         <v>15</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
@@ -4755,7 +4822,7 @@
         <v>8</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>2</v>
@@ -4797,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -4847,55 +4914,55 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
         <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.524</v>
+        <v>0.516</v>
       </c>
       <c r="H25" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="J25" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K25" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O25" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P25" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0.766</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -4919,16 +4986,16 @@
         <v>20.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
         <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4940,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
@@ -4958,7 +5025,7 @@
         <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP25" t="n">
         <v>24</v>
@@ -4973,7 +5040,7 @@
         <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5131,7 +5198,7 @@
         <v>12</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM26" t="n">
         <v>19</v>
@@ -5152,7 +5219,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5173,16 +5240,16 @@
         <v>27</v>
       </c>
       <c r="AZ26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>4</v>
@@ -5301,13 +5368,13 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
@@ -5316,7 +5383,7 @@
         <v>6</v>
       </c>
       <c r="AM27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN27" t="n">
         <v>5</v>
@@ -5325,7 +5392,7 @@
         <v>26</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ27" t="n">
         <v>13</v>
@@ -5334,13 +5401,13 @@
         <v>24</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
         <v>17</v>
       </c>
       <c r="AU27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV27" t="n">
         <v>5</v>
@@ -5358,13 +5425,13 @@
         <v>2</v>
       </c>
       <c r="BA27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB27" t="n">
         <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5483,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5501,7 +5568,7 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO28" t="n">
         <v>25</v>
@@ -5513,7 +5580,7 @@
         <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5540,7 +5607,7 @@
         <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB28" t="n">
         <v>18</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5671,13 +5738,13 @@
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5701,7 +5768,7 @@
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" t="n">
         <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.656</v>
+        <v>0.651</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J30" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.497</v>
+        <v>0.495</v>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.368</v>
+        <v>0.361</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
         <v>28.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R30" t="n">
         <v>11.4</v>
@@ -5808,7 +5875,7 @@
         <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
@@ -5823,22 +5890,22 @@
         <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AA30" t="n">
         <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.3</v>
+        <v>105.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>7</v>
@@ -5865,10 +5932,10 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
@@ -5939,34 +6006,34 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.484</v>
+        <v>0.492</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K31" t="n">
         <v>0.441</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N31" t="n">
         <v>0.34</v>
@@ -5975,10 +6042,10 @@
         <v>19.3</v>
       </c>
       <c r="P31" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.793</v>
+        <v>0.794</v>
       </c>
       <c r="R31" t="n">
         <v>12.4</v>
@@ -5990,7 +6057,7 @@
         <v>42.1</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V31" t="n">
         <v>13.6</v>
@@ -6005,10 +6072,10 @@
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB31" t="n">
         <v>98.09999999999999</v>
@@ -6017,7 +6084,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6032,13 +6099,13 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,13 +6114,13 @@
         <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
         <v>3</v>
@@ -6083,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-8-2007-08</t>
+          <t>2008-03-08</t>
         </is>
       </c>
     </row>
